--- a/Result/profitability/1795.xlsx
+++ b/Result/profitability/1795.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>3.8425</v>
+        <v>3.40375</v>
       </c>
       <c r="N2" t="n">
-        <v>58.51125</v>
+        <v>57.30375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>3.13</v>
+        <v>2.8975</v>
       </c>
       <c r="N3" t="n">
-        <v>58.64625</v>
+        <v>58.4775</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6825</v>
+        <v>2.3075</v>
       </c>
       <c r="N4" t="n">
-        <v>59.8275</v>
+        <v>58.8325</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.2</v>
       </c>
       <c r="M5" t="n">
-        <v>2.02375</v>
+        <v>1.98125</v>
       </c>
       <c r="N5" t="n">
-        <v>59.92375</v>
+        <v>59.27875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.7</v>
       </c>
       <c r="M6" t="n">
-        <v>1.585</v>
+        <v>1.2025</v>
       </c>
       <c r="N6" t="n">
-        <v>59.88</v>
+        <v>59.425</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.46</v>
       </c>
       <c r="M7" t="n">
-        <v>0.95125</v>
+        <v>0.7212500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>60.56625</v>
+        <v>60.3625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.23</v>
       </c>
       <c r="M8" t="n">
-        <v>0.44125</v>
+        <v>0.4775</v>
       </c>
       <c r="N8" t="n">
-        <v>61.05375</v>
+        <v>61.4225</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0.12125</v>
       </c>
       <c r="N10" t="n">
-        <v>59.68750000000001</v>
+        <v>59.6875</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8809</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4080</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4728</v>
+      </c>
+      <c r="F75" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2333</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>26.49%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1343</v>
+      </c>
+      <c r="J75" t="n">
+        <v>990</v>
+      </c>
+      <c r="K75" t="n">
+        <v>642</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M75" t="n">
+        <v>4.135</v>
+      </c>
+      <c r="N75" t="n">
+        <v>56.98625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1330275229357798</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.950000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05815099546619362</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.3399999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1209964412811387</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.160000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08769544527532291</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
